--- a/Research Logs/Matt/Matt Baker - Week 9 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 9 Research Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA3D73F-412A-4997-83E7-6D5D1B69DC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D20A2-99B0-425D-A82D-3973CEBBA8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2385" yWindow="2940" windowWidth="30180" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -470,6 +470,18 @@
     <t>https://www.youtube.com/watch?v=2Fp1N6dof0Y
 https://www.youtube.com/watch?v=yeH3rw3rgHA
 https://www.youtube.com/watch?v=EOb37Oug_cw</t>
+  </si>
+  <si>
+    <t>Trying to engineer the integration of "prompt chunking" into my script so that I can split the large "audit.txt" text files into managable chunks in order to no exceed the context length and have the LLM miss important contextual information</t>
+  </si>
+  <si>
+    <t>Google, GitHub
+https://gist.github.com/simbo1905/053b48269b1e95800500b85190adf427
+https://dev.to/simbo1905/genai-test-file-summarisation-in-chunks-with-ollama-or-cloud-b52
+https://github.com/rayhanfay/agentic-chunking</t>
+  </si>
+  <si>
+    <t>These prebuilt solutions are far more complex than is necessary, my use case is not enterprise-scale. Examining these scripts and processes however gave me the idea to just look for a linux command (split) that can actually just halve the audit.txt file and summarize both in my own way.</t>
   </si>
 </sst>
 </file>
@@ -838,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G51"/>
+  <dimension ref="B2:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
@@ -855,7 +867,7 @@
       </c>
       <c r="D2" s="5">
         <f>ROUNDDOWN(SUM(C6:C499)/60,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1601,6 +1613,26 @@
       </c>
       <c r="G51" s="6" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B52" s="3">
+        <v>46277</v>
+      </c>
+      <c r="C52">
+        <v>60</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
